--- a/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-01/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_SERVICE_GAS_ONE_ΜΟΝ._Α.Ε_2026-01.xlsx
+++ b/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-01/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_SERVICE_GAS_ONE_ΜΟΝ._Α.Ε_2026-01.xlsx
@@ -699,7 +699,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -973,6 +973,15 @@
     </xf>
     <xf numFmtId="168" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="11" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2835,7 +2844,7 @@
     <row r="6" ht="60.75" customFormat="1" customHeight="1" s="10">
       <c r="B6" s="80" t="inlineStr">
         <is>
-          <t>13/02/26</t>
+          <t>06/03/26</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -3324,36 +3333,36 @@
         </is>
       </c>
       <c r="D30" s="25" t="n">
-        <v>959.1</v>
+        <v>21046.32</v>
       </c>
       <c r="E30" s="25" t="n">
-        <v>104.2802832</v>
+        <v>2272.4473527</v>
       </c>
       <c r="F30" s="25" t="n">
-        <v>0.24</v>
+        <v>5.26</v>
       </c>
       <c r="G30" s="92" t="n">
-        <v>108.73</v>
+        <v>107.97</v>
       </c>
       <c r="H30" s="93" t="n"/>
     </row>
     <row r="31" ht="28.5" customHeight="1" s="76">
-      <c r="C31" s="91" t="inlineStr">
+      <c r="C31" s="94" t="inlineStr">
         <is>
           <t>Σύνολο</t>
         </is>
       </c>
-      <c r="D31" s="25" t="n">
-        <v>461103.63</v>
-      </c>
-      <c r="E31" s="25" t="n">
-        <v>55142.19</v>
-      </c>
-      <c r="F31" s="25" t="n">
-        <v>115.26</v>
-      </c>
-      <c r="G31" s="92" t="n">
-        <v>119.59</v>
+      <c r="D31" s="95" t="n">
+        <v>481190.85</v>
+      </c>
+      <c r="E31" s="95" t="n">
+        <v>57310.36</v>
+      </c>
+      <c r="F31" s="95" t="n">
+        <v>120.28</v>
+      </c>
+      <c r="G31" s="96" t="n">
+        <v>119.1</v>
       </c>
       <c r="H31" s="93" t="n"/>
     </row>
@@ -3362,7 +3371,7 @@
       <c r="D32" s="25" t="n"/>
       <c r="E32" s="26" t="n"/>
       <c r="F32" s="27" t="n"/>
-      <c r="G32" s="94" t="n"/>
+      <c r="G32" s="97" t="n"/>
       <c r="H32" s="93" t="n"/>
     </row>
     <row r="33" ht="28.5" customHeight="1" s="76">
@@ -3370,7 +3379,7 @@
       <c r="D33" s="25" t="n"/>
       <c r="E33" s="26" t="n"/>
       <c r="F33" s="27" t="n"/>
-      <c r="G33" s="94" t="n"/>
+      <c r="G33" s="97" t="n"/>
       <c r="H33" s="93" t="n"/>
     </row>
     <row r="34" ht="28.5" customHeight="1" s="76">
@@ -3378,7 +3387,7 @@
       <c r="D34" s="25" t="n"/>
       <c r="E34" s="26" t="n"/>
       <c r="F34" s="27" t="n"/>
-      <c r="G34" s="94" t="n"/>
+      <c r="G34" s="97" t="n"/>
       <c r="H34" s="93" t="n"/>
     </row>
     <row r="35" ht="28.5" customHeight="1" s="76">
@@ -3386,7 +3395,7 @@
       <c r="D35" s="25" t="n"/>
       <c r="E35" s="26" t="n"/>
       <c r="F35" s="27" t="n"/>
-      <c r="G35" s="94" t="n"/>
+      <c r="G35" s="97" t="n"/>
       <c r="H35" s="93" t="n"/>
     </row>
     <row r="36" ht="28.5" customHeight="1" s="76">
@@ -3394,7 +3403,7 @@
       <c r="D36" s="25" t="n"/>
       <c r="E36" s="26" t="n"/>
       <c r="F36" s="27" t="n"/>
-      <c r="G36" s="94" t="n"/>
+      <c r="G36" s="97" t="n"/>
       <c r="H36" s="93" t="n"/>
     </row>
     <row r="37" ht="28.5" customHeight="1" s="76">
@@ -3402,7 +3411,7 @@
       <c r="D37" s="25" t="n"/>
       <c r="E37" s="26" t="n"/>
       <c r="F37" s="27" t="n"/>
-      <c r="G37" s="94" t="n"/>
+      <c r="G37" s="97" t="n"/>
       <c r="H37" s="93" t="n"/>
     </row>
     <row r="38" ht="28.5" customHeight="1" s="76">
@@ -3410,7 +3419,7 @@
       <c r="D38" s="25" t="n"/>
       <c r="E38" s="26" t="n"/>
       <c r="F38" s="27" t="n"/>
-      <c r="G38" s="94" t="n"/>
+      <c r="G38" s="97" t="n"/>
       <c r="H38" s="93" t="n"/>
     </row>
     <row r="39" ht="28.5" customHeight="1" s="76">
@@ -3418,7 +3427,7 @@
       <c r="D39" s="25" t="n"/>
       <c r="E39" s="26" t="n"/>
       <c r="F39" s="27" t="n"/>
-      <c r="G39" s="94" t="n"/>
+      <c r="G39" s="97" t="n"/>
       <c r="H39" s="93" t="n"/>
     </row>
     <row r="40" ht="28.5" customHeight="1" s="76">
@@ -3426,7 +3435,7 @@
       <c r="D40" s="25" t="n"/>
       <c r="E40" s="26" t="n"/>
       <c r="F40" s="27" t="n"/>
-      <c r="G40" s="94" t="n"/>
+      <c r="G40" s="97" t="n"/>
       <c r="H40" s="93" t="n"/>
     </row>
     <row r="41" ht="28.5" customHeight="1" s="76" thickBot="1">
@@ -3434,7 +3443,7 @@
       <c r="D41" s="30" t="n"/>
       <c r="E41" s="30" t="n"/>
       <c r="F41" s="31" t="n"/>
-      <c r="G41" s="95" t="n"/>
+      <c r="G41" s="98" t="n"/>
       <c r="H41" s="93" t="n"/>
     </row>
     <row r="42" ht="28.5" customHeight="1" s="76">
@@ -3442,7 +3451,7 @@
       <c r="D42" s="33" t="n"/>
       <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="n"/>
-      <c r="G42" s="96" t="n"/>
+      <c r="G42" s="99" t="n"/>
       <c r="H42" s="93" t="n"/>
     </row>
     <row r="43" ht="49" customHeight="1" s="76" thickBot="1">
@@ -3456,16 +3465,16 @@
           <t>Ανάλυση Χρεώσεων και Υπηρεσίων ΦοΣΕ</t>
         </is>
       </c>
-      <c r="C44" s="97" t="n"/>
-      <c r="D44" s="98" t="n"/>
+      <c r="C44" s="100" t="n"/>
+      <c r="D44" s="101" t="n"/>
       <c r="E44" s="18" t="n"/>
-      <c r="F44" s="99" t="inlineStr">
+      <c r="F44" s="102" t="inlineStr">
         <is>
           <t>Υπολογισμός προς καταβολή</t>
         </is>
       </c>
-      <c r="G44" s="97" t="n"/>
-      <c r="H44" s="100" t="n"/>
+      <c r="G44" s="100" t="n"/>
+      <c r="H44" s="103" t="n"/>
       <c r="I44" s="45" t="n"/>
     </row>
     <row r="45" ht="36" customHeight="1" s="76">
@@ -3475,7 +3484,7 @@
         </is>
       </c>
       <c r="C45" s="83" t="n"/>
-      <c r="D45" s="101" t="n">
+      <c r="D45" s="104" t="n">
         <v>0.25</v>
       </c>
       <c r="E45" s="44" t="n"/>
@@ -3485,8 +3494,8 @@
         </is>
       </c>
       <c r="G45" s="83" t="n"/>
-      <c r="H45" s="102" t="n">
-        <v>461.1</v>
+      <c r="H45" s="105" t="n">
+        <v>481.19</v>
       </c>
       <c r="I45" s="45" t="n"/>
     </row>
@@ -3496,9 +3505,9 @@
           <t>Σύνολο (€)</t>
         </is>
       </c>
-      <c r="C46" s="103" t="n"/>
-      <c r="D46" s="104" t="n">
-        <v>115.26</v>
+      <c r="C46" s="106" t="n"/>
+      <c r="D46" s="107" t="n">
+        <v>120.28</v>
       </c>
       <c r="E46" s="41" t="n"/>
       <c r="F46" s="60" t="inlineStr">
@@ -3507,8 +3516,8 @@
         </is>
       </c>
       <c r="G46" s="83" t="n"/>
-      <c r="H46" s="102" t="n">
-        <v>55142.19</v>
+      <c r="H46" s="105" t="n">
+        <v>57310.36</v>
       </c>
       <c r="I46" s="45" t="n"/>
     </row>
@@ -3547,7 +3556,7 @@
           <t xml:space="preserve">Συνολικό Ποσό προς καταβολή </t>
         </is>
       </c>
-      <c r="G49" s="103" t="n"/>
+      <c r="G49" s="106" t="n"/>
       <c r="H49" s="48">
         <f>H46+H47+H48</f>
         <v/>
@@ -3568,16 +3577,16 @@
           <t>Στοιχεία Τράπεζας</t>
         </is>
       </c>
-      <c r="C51" s="97" t="n"/>
-      <c r="D51" s="98" t="n"/>
+      <c r="C51" s="100" t="n"/>
+      <c r="D51" s="101" t="n"/>
       <c r="E51" s="41" t="n"/>
-      <c r="F51" s="99" t="inlineStr">
+      <c r="F51" s="102" t="inlineStr">
         <is>
           <t>Υπολογισμός Τιμολόγησης</t>
         </is>
       </c>
-      <c r="G51" s="97" t="n"/>
-      <c r="H51" s="100" t="n"/>
+      <c r="G51" s="100" t="n"/>
+      <c r="H51" s="103" t="n"/>
       <c r="I51" s="45" t="n"/>
     </row>
     <row r="52" ht="25.25" customHeight="1" s="76">
@@ -3586,12 +3595,12 @@
           <t xml:space="preserve"> ΙΒΑΝ</t>
         </is>
       </c>
-      <c r="C52" s="105" t="inlineStr">
+      <c r="C52" s="108" t="inlineStr">
         <is>
           <t>GR0801721480005148115670536</t>
         </is>
       </c>
-      <c r="D52" s="106" t="n"/>
+      <c r="D52" s="109" t="n"/>
       <c r="E52" s="41" t="n"/>
       <c r="F52" s="60" t="inlineStr">
         <is>
@@ -3611,12 +3620,12 @@
           <t xml:space="preserve"> Ημερομηνία</t>
         </is>
       </c>
-      <c r="C53" s="107" t="inlineStr">
-        <is>
-          <t>15/02/26</t>
-        </is>
-      </c>
-      <c r="D53" s="108" t="n"/>
+      <c r="C53" s="110" t="inlineStr">
+        <is>
+          <t>08/03/26</t>
+        </is>
+      </c>
+      <c r="D53" s="111" t="n"/>
       <c r="E53" s="41" t="n"/>
       <c r="F53" s="60" t="inlineStr">
         <is>
@@ -3640,7 +3649,7 @@
           <t xml:space="preserve">ΓΕΝΙΚΟ ΣΥΝΟΛΟ </t>
         </is>
       </c>
-      <c r="G54" s="103" t="n"/>
+      <c r="G54" s="106" t="n"/>
       <c r="H54" s="43">
         <f>H52+H53</f>
         <v/>
@@ -3649,7 +3658,7 @@
     </row>
     <row r="55" ht="28.75" customHeight="1" s="76"/>
     <row r="56" ht="38.25" customHeight="1" s="76">
-      <c r="B56" s="109" t="inlineStr">
+      <c r="B56" s="112" t="inlineStr">
         <is>
           <t>Σημείωση: Το τελικό ποσό πίστωσης παραγωγού προκύπτει από το άθροισμα των γινομένων της παραγόμενης ενέργειας επί της αντίστοιχης Τιμής Εκκαθάρισης Αγοράς Επόμενης Ημέρας ανά 15', αφαιρώντας την πληρωμή υπηρεσιών ΦοΣΕ και Διαχειριστικών εξόδων. Οι πληρωμές της GREEN VALUE Α.Ε. πραγματοποιουνται εντός 2 εργάσιμων ημερών μετά την παραλαβή του ενημερωτικού σημειώματος.</t>
         </is>
